--- a/output/pdf_financials_xlsx/ARM.xlsx
+++ b/output/pdf_financials_xlsx/ARM.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.209629</v>
+        <v>0.222504</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.121829</v>
+        <v>5.195979</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.032246</v>
+        <v>0.114319</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.003054</v>
+        <v>-0.015929</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.037594</v>
+        <v>-5.036556</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.124176</v>
+        <v>0.042103</v>
       </c>
     </row>
     <row r="12">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARM.xlsx
+++ b/output/pdf_financials_xlsx/ARM.xlsx
@@ -676,10 +676,10 @@
         <v>-0.015929</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-5.0343</v>
+        <v>-5.032044</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.008791</v>
+        <v>-0.024521</v>
       </c>
     </row>
     <row r="17">
@@ -692,10 +692,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.002256</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.033312</v>
       </c>
     </row>
     <row r="18">
@@ -868,10 +868,10 @@
         <v>-0.015929</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.0343</v>
+        <v>-5.032044</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.008791</v>
+        <v>-0.024521</v>
       </c>
     </row>
     <row r="28">
@@ -900,10 +900,10 @@
         <v>-0.015929</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.0343</v>
+        <v>-5.032044</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.008791</v>
+        <v>-0.024521</v>
       </c>
     </row>
     <row r="30">
@@ -916,10 +916,10 @@
         <v>-7.711000847149946</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-3157.825407877157</v>
+        <v>-3156.410304661184</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.620053445167559</v>
+        <v>-15.67618365703034</v>
       </c>
     </row>
     <row r="31">
@@ -932,10 +932,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.04483267634384755</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-135.8509033073692</v>
       </c>
     </row>
     <row r="32">
@@ -4957,7 +4957,11 @@
           <t>Income taxes recovery (expenses)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5352,7 +5356,11 @@
           <t>Income taxes recovery (expenses)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
